--- a/static/templates/home-charging-template.xlsx
+++ b/static/templates/home-charging-template.xlsx
@@ -100,7 +100,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="$#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="$#,##0.00000"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
     <numFmt numFmtId="167" formatCode="$#,##0.00"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>

--- a/static/templates/home-charging-template.xlsx
+++ b/static/templates/home-charging-template.xlsx
@@ -175,22 +175,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -543,7 +558,7 @@
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -616,7 +631,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>14</v>
       </c>
@@ -629,11 +644,11 @@
       <c r="D8" s="10">
         <v>8.2</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>16</v>
       </c>
@@ -646,11 +661,11 @@
       <c r="D9" s="10">
         <v>7.9</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>17</v>
       </c>
@@ -663,27 +678,27 @@
       <c r="D10" s="10">
         <v>9.1</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="12">
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="13">
         <f>SUM(D8:D10)</f>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="13">
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="14">
         <f>D11*E4</f>
       </c>
     </row>
@@ -713,7 +728,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>21</v>
       </c>
@@ -726,11 +741,11 @@
       <c r="D16" s="10">
         <v>12.4</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="11" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>23</v>
       </c>
@@ -743,27 +758,27 @@
       <c r="D17" s="10">
         <v>10.8</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="12">
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="13">
         <f>SUM(D16:D17)</f>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="14">
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="15">
         <f>D11/(D11+D18)</f>
       </c>
     </row>

--- a/static/templates/home-charging-template.xlsx
+++ b/static/templates/home-charging-template.xlsx
@@ -98,12 +98,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="$#,##0.00000"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="$#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -197,7 +196,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -210,8 +209,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/static/templates/home-charging-template.xlsx
+++ b/static/templates/home-charging-template.xlsx
@@ -127,6 +127,8 @@
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="16"/>
     </font>
   </fonts>
   <fills count="4">
@@ -174,10 +176,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -205,12 +209,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -681,7 +695,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>18</v>
       </c>
@@ -691,7 +705,7 @@
         <f>SUM(D8:D10)</f>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>19</v>
       </c>
@@ -761,7 +775,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>25</v>
       </c>
@@ -771,15 +785,16 @@
         <f>SUM(D16:D17)</f>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+    <row r="20" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="15">
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="16">
         <f>D11/(D11+D18)</f>
       </c>
+      <c r="E20" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/static/templates/home-charging-template.xlsx
+++ b/static/templates/home-charging-template.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
   <si>
     <t>Full Name:</t>
   </si>
@@ -92,6 +92,9 @@
   </si>
   <si>
     <t>Percentage of Home Charging:</t>
+  </si>
+  <si>
+    <t>Report generated by ev-charging-log — https://github.com/brianramseyau/ev-charging-log</t>
   </si>
 </sst>
 </file>
@@ -104,7 +107,7 @@
     <numFmt numFmtId="166" formatCode="$#,##0.00"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -129,6 +132,12 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="16"/>
+    </font>
+    <font>
+      <i/>
+      <u/>
+      <color rgb="FF64748B"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -176,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -225,6 +234,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -564,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -796,15 +808,28 @@
       </c>
       <c r="E20" s="17"/>
     </row>
+    <row r="22" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A22:E22"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A22" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
